--- a/Data/Inputs/fluids.xlsx
+++ b/Data/Inputs/fluids.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f50a7c5896c0110/Documents/GitHub/S3D_Senior_Design/Data/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_2B59D2BFD3E051E8451687B24C3088B35299F368" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E9E6146-8D75-4410-ACAB-A10D83462F16}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_2B59D2BFD3E051E8451687B24C3088B35299F368" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{484BCB1B-B6E6-4D60-89A1-78F2D42A4275}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51720" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FLUID_LIBRARY" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>fluid_id</t>
   </si>
@@ -77,6 +77,51 @@
   </si>
   <si>
     <t>HFE_7100</t>
+  </si>
+  <si>
+    <t>Propylene Glycol/Water 30%</t>
+  </si>
+  <si>
+    <t>Polyalphaolefin 6 cSt</t>
+  </si>
+  <si>
+    <t>3M Novec 7100</t>
+  </si>
+  <si>
+    <t>water_glycol</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
+    <t>dielectric</t>
+  </si>
+  <si>
+    <t>metals_ok</t>
+  </si>
+  <si>
+    <t>check elastomers</t>
+  </si>
+  <si>
+    <t>good dielectric</t>
+  </si>
+  <si>
+    <t>low cp</t>
+  </si>
+  <si>
+    <t>higher dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">common test flui </t>
+  </si>
+  <si>
+    <t>vendor/handbook</t>
+  </si>
+  <si>
+    <t>vendor</t>
+  </si>
+  <si>
+    <t>datasheet</t>
   </si>
 </sst>
 </file>
@@ -473,15 +518,150 @@
       <c r="A2" t="s">
         <v>16</v>
       </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2">
+        <v>1035</v>
+      </c>
+      <c r="E2">
+        <v>3800</v>
+      </c>
+      <c r="F2">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="G2">
+        <v>0.45</v>
+      </c>
+      <c r="H2">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="I2">
+        <v>-12</v>
+      </c>
+      <c r="J2">
+        <v>104</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>80</v>
+      </c>
+      <c r="M2">
+        <v>-10</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>17</v>
       </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3">
+        <v>830</v>
+      </c>
+      <c r="E3">
+        <v>2100</v>
+      </c>
+      <c r="F3">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G3">
+        <v>0.13</v>
+      </c>
+      <c r="H3">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="I3">
+        <v>-60</v>
+      </c>
+      <c r="J3">
+        <v>300</v>
+      </c>
+      <c r="K3">
+        <v>0.1</v>
+      </c>
+      <c r="L3">
+        <v>120</v>
+      </c>
+      <c r="M3">
+        <v>-40</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>1500</v>
+      </c>
+      <c r="E4">
+        <v>1200</v>
+      </c>
+      <c r="F4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="G4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H4">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="I4">
+        <v>-135</v>
+      </c>
+      <c r="J4">
+        <v>61</v>
+      </c>
+      <c r="K4">
+        <v>27</v>
+      </c>
+      <c r="L4">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>-80</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
